--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_307_R31.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_307_R31.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.2054</v>
+        <v>5.7343</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0573</v>
+        <v>4.8214</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1481</v>
+        <v>0.9129</v>
       </c>
       <c r="G2" t="n">
         <v>3.3243</v>
@@ -610,13 +610,13 @@
         <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5074</v>
+        <v>0.0362</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4288</v>
+        <v>0.1928</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0786</v>
+        <v>-0.1566</v>
       </c>
       <c r="V2" t="n">
         <v>1.214</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.1313</v>
+        <v>5.7211</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2911</v>
+        <v>2.8808</v>
       </c>
       <c r="F3" t="n">
         <v>2.8402</v>
@@ -688,10 +688,10 @@
         <v>2.3195</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8768</v>
+        <v>-0.2871</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8725000000000001</v>
+        <v>-0.2827</v>
       </c>
       <c r="U3" t="n">
         <v>-0.0044</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8436</v>
+        <v>2.9965</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8328</v>
+        <v>-0.2431</v>
       </c>
       <c r="F4" t="n">
-        <v>3.6764</v>
+        <v>3.2395</v>
       </c>
       <c r="G4" t="n">
         <v>2.4012</v>
@@ -766,13 +766,13 @@
         <v>3.0154</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0242</v>
+        <v>0.1287</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5342</v>
+        <v>0.0556</v>
       </c>
       <c r="U4" t="n">
-        <v>0.51</v>
+        <v>0.0732</v>
       </c>
       <c r="V4" t="n">
         <v>0.9304</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0065</v>
+        <v>1.8953</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1599</v>
+        <v>0.8807</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8466</v>
+        <v>1.0147</v>
       </c>
       <c r="G5" t="n">
         <v>0.4866</v>
@@ -844,13 +844,13 @@
         <v>0.6959</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9142</v>
+        <v>0.803</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0578</v>
+        <v>0.7786999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1436</v>
+        <v>0.0244</v>
       </c>
       <c r="V5" t="n">
         <v>0.1418</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0954</v>
+        <v>0.1928</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.286</v>
+        <v>-1.1549</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3813</v>
+        <v>1.3477</v>
       </c>
       <c r="G6" t="n">
         <v>-0.2743</v>
@@ -922,13 +922,13 @@
         <v>1.3917</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2278</v>
+        <v>0.3253</v>
       </c>
       <c r="T6" t="n">
-        <v>1.5454</v>
+        <v>0.6765</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3176</v>
+        <v>-0.3512</v>
       </c>
       <c r="V6" t="n">
         <v>0.1418</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. BOLOMBOY</t>
+          <t>D. MOTIEJUNAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.265</v>
+        <v>0.1914</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.398</v>
+        <v>0.1943</v>
       </c>
       <c r="F7" t="n">
-        <v>1.663</v>
+        <v>-0.0029</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7927999999999999</v>
+        <v>-0.4048</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5451</v>
+        <v>0.1741</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2477</v>
+        <v>-0.5788</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4532</v>
+        <v>0.0168</v>
       </c>
       <c r="K7" t="n">
-        <v>0.306</v>
+        <v>0.0168</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1472</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3396</v>
+        <v>-0.4216</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2391</v>
+        <v>0.1573</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1005</v>
+        <v>-0.5788</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.0876</v>
+        <v>0.4639</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="S7" t="n">
-        <v>2.0959</v>
+        <v>-0.1513</v>
       </c>
       <c r="T7" t="n">
-        <v>1.628</v>
+        <v>-0.1061</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4679</v>
+        <v>-0.0452</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5361</v>
+        <v>0.2836</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2836</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. MOTIEJUNAS</t>
+          <t>J. BOLOMBOY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0062</v>
+        <v>-0.8391999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>0.07630000000000001</v>
+        <v>-2.267</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0701</v>
+        <v>1.4278</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4048</v>
+        <v>0.7927999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1741</v>
+        <v>0.5451</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5788</v>
+        <v>0.2477</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0168</v>
+        <v>0.4532</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0168</v>
+        <v>0.306</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.1472</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4216</v>
+        <v>0.3396</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1573</v>
+        <v>0.2391</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5788</v>
+        <v>0.1005</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4639</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4639</v>
+        <v>1.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3365</v>
+        <v>0.9917</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.224</v>
+        <v>0.7591</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1125</v>
+        <v>0.2326</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2836</v>
+        <v>-0.5361</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2836</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. NWORA</t>
+          <t>T. CARTER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0059</v>
+        <v>-0.8678</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.8673</v>
+        <v>-0.9582000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>2.8614</v>
+        <v>0.0905</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.6192</v>
+        <v>-0.4766</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.5585</v>
+        <v>-0.0048</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0607</v>
+        <v>-0.4718</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.9231</v>
+        <v>-0.7695</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.925</v>
+        <v>0.0168</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.9982</v>
+        <v>-0.7863</v>
       </c>
       <c r="M9" t="n">
-        <v>1.304</v>
+        <v>0.293</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6335</v>
+        <v>-0.0216</v>
       </c>
       <c r="O9" t="n">
-        <v>1.9375</v>
+        <v>0.3145</v>
       </c>
       <c r="P9" t="n">
-        <v>1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1598</v>
+        <v>-0.232</v>
       </c>
       <c r="R9" t="n">
-        <v>2.5515</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1494</v>
+        <v>-0.1592</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0712</v>
+        <v>0.0433</v>
       </c>
       <c r="U9" t="n">
-        <v>0.07820000000000001</v>
+        <v>-0.2025</v>
       </c>
       <c r="V9" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. CARTER</t>
+          <t>J. NWORA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0529</v>
+        <v>-0.9312</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0762</v>
+        <v>-3.7926</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0232</v>
+        <v>2.8614</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4766</v>
+        <v>-3.6192</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0048</v>
+        <v>-2.5585</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4718</v>
+        <v>-1.0607</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7695</v>
+        <v>-4.9231</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0168</v>
+        <v>-1.925</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7863</v>
+        <v>-2.9982</v>
       </c>
       <c r="M10" t="n">
-        <v>0.293</v>
+        <v>1.304</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0216</v>
+        <v>-0.6335</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3145</v>
+        <v>1.9375</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.5515</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3444</v>
+        <v>0.224</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0747</v>
+        <v>0.1458</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2697</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6146</v>
+        <v>-1.1771</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1508</v>
+        <v>-1.9149</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5361</v>
+        <v>0.7378</v>
       </c>
       <c r="G11" t="n">
         <v>-0.8292</v>
@@ -1312,13 +1312,13 @@
         <v>1.1598</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7855</v>
+        <v>-0.3479</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3655</v>
+        <v>-0.1296</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.42</v>
+        <v>-0.2183</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.7248</v>
+        <v>-3.3875</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.2503</v>
+        <v>-3.3499</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4745</v>
+        <v>-0.0376</v>
       </c>
       <c r="G12" t="n">
         <v>-1.944</v>
@@ -1390,13 +1390,13 @@
         <v>1.8556</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.4071</v>
+        <v>-0.0698</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5737</v>
+        <v>0.3266</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8333</v>
+        <v>-0.3965</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6778999999999999</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.155200000000001</v>
+        <v>9.528600000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.276800000000001</v>
+        <v>-4.9034</v>
       </c>
       <c r="F13" t="n">
-        <v>14.4317</v>
+        <v>14.432</v>
       </c>
       <c r="G13" t="n">
         <v>1.9315</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.6784999999999997</v>
+        <v>-0.6785000000000001</v>
       </c>
       <c r="I13" t="n">
         <v>2.6103</v>
@@ -1468,13 +1468,13 @@
         <v>16.2367</v>
       </c>
       <c r="S13" t="n">
-        <v>1.1202</v>
+        <v>1.4936</v>
       </c>
       <c r="T13" t="n">
-        <v>2.0866</v>
+        <v>2.46</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9664</v>
+        <v>-0.9663000000000002</v>
       </c>
       <c r="V13" t="n">
         <v>3.7838</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.5923</v>
+        <v>4.7952</v>
       </c>
       <c r="E14" t="n">
         <v>3.1582</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4341</v>
+        <v>1.637</v>
       </c>
       <c r="G14" t="n">
         <v>3.3</v>
@@ -1546,13 +1546,13 @@
         <v>2.0876</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0299</v>
+        <v>0.1731</v>
       </c>
       <c r="T14" t="n">
         <v>0.0949</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1247</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>0.3943</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8499</v>
+        <v>2.1194</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9163</v>
+        <v>1.1522</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9336</v>
+        <v>0.9671999999999999</v>
       </c>
       <c r="G15" t="n">
         <v>1.6781</v>
@@ -1624,13 +1624,13 @@
         <v>0.6959</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2921</v>
+        <v>-0.0226</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1336</v>
+        <v>0.1024</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1586</v>
+        <v>-0.125</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K. BIRCH</t>
+          <t>M. BIRSEN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2798</v>
+        <v>1.0627</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3965</v>
+        <v>0.0988</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1167</v>
+        <v>0.9639</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7712</v>
+        <v>0.5836</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9651999999999999</v>
+        <v>0.8044</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1939</v>
+        <v>-0.2208</v>
       </c>
       <c r="J16" t="n">
-        <v>1.4719</v>
+        <v>0.2515</v>
       </c>
       <c r="K16" t="n">
-        <v>1.3983</v>
+        <v>0.8907</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0736</v>
+        <v>-0.6391</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7007</v>
+        <v>0.3321</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4331</v>
+        <v>-0.0862</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2676</v>
+        <v>0.4183</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9278</v>
+        <v>0.9278</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.3195</v>
+        <v>-0.232</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S16" t="n">
-        <v>2.9029</v>
+        <v>0.4817</v>
       </c>
       <c r="T16" t="n">
-        <v>2.6384</v>
+        <v>-0.0626</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2645</v>
+        <v>0.5443</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.4665</v>
+        <v>-0.9304</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.3943</v>
+        <v>0.1418</v>
       </c>
       <c r="X16" t="n">
         <v>-1.0722</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. BIRSEN</t>
+          <t>W. BALDWIN IV</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1134</v>
+        <v>-0.1853</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2167</v>
+        <v>-1.5639</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8967000000000001</v>
+        <v>1.3786</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5836</v>
+        <v>2.1884</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8044</v>
+        <v>0.7765</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2208</v>
+        <v>1.4119</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2515</v>
+        <v>0.9164</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8907</v>
+        <v>0.6021</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6391</v>
+        <v>0.3143</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3321</v>
+        <v>1.272</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0862</v>
+        <v>0.1744</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4183</v>
+        <v>1.0976</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9278</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.232</v>
+        <v>-2.3195</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5324</v>
+        <v>-0.4639</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0553</v>
+        <v>-0.1608</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4771</v>
+        <v>-0.3031</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9304</v>
+        <v>-1.214</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0722</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9353</v>
+        <v>-0.5313</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9530999999999999</v>
+        <v>-0.7171999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0179</v>
+        <v>0.1859</v>
       </c>
       <c r="G18" t="n">
         <v>-0.06560000000000001</v>
@@ -1858,13 +1858,13 @@
         <v>0.4639</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2614</v>
+        <v>0.1426</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2908</v>
+        <v>-0.0549</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0294</v>
+        <v>0.1975</v>
       </c>
       <c r="V18" t="n">
         <v>-1.0722</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. SILVA</t>
+          <t>K. BIRCH</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2236</v>
+        <v>-0.6226</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5355</v>
+        <v>-0.3728</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3119</v>
+        <v>-0.2498</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2111</v>
+        <v>0.7712</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.994</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>0.783</v>
+        <v>-0.1939</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1572</v>
+        <v>1.4719</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.7829</v>
+        <v>1.3983</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6257</v>
+        <v>0.0736</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0539</v>
+        <v>-0.7007</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2112</v>
+        <v>-0.4331</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1573</v>
+        <v>-0.2676</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.1598</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.3917</v>
+        <v>-2.3195</v>
       </c>
       <c r="R19" t="n">
-        <v>0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0365</v>
+        <v>1.0005</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5228</v>
+        <v>0.8691</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5592</v>
+        <v>0.1314</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1107</v>
+        <v>-1.4665</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5361</v>
+        <v>-0.3943</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.4254</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6096</v>
+        <v>-1.0662</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5486</v>
+        <v>-1.6666</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0609</v>
+        <v>0.6004</v>
       </c>
       <c r="G20" t="n">
         <v>-4.1457</v>
@@ -2014,13 +2014,13 @@
         <v>1.8556</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2139</v>
+        <v>0.3295</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3189</v>
+        <v>0.201</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5329</v>
+        <v>0.1285</v>
       </c>
       <c r="V20" t="n">
         <v>2.2862</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>W. BALDWIN IV</t>
+          <t>C. SILVA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0269</v>
+        <v>-1.436</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5075</v>
+        <v>-1.5355</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4806</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>2.1884</v>
+        <v>-0.2111</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7765</v>
+        <v>-0.994</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4119</v>
+        <v>0.783</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9164</v>
+        <v>-0.1572</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6021</v>
+        <v>-0.7829</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3143</v>
+        <v>0.6257</v>
       </c>
       <c r="M21" t="n">
-        <v>1.272</v>
+        <v>-0.0539</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1744</v>
+        <v>-0.2112</v>
       </c>
       <c r="O21" t="n">
-        <v>1.0976</v>
+        <v>0.1573</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6959</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.3195</v>
+        <v>-1.3917</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6237</v>
+        <v>0.232</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.3054</v>
+        <v>-0.1759</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1044</v>
+        <v>-0.5228</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.201</v>
+        <v>0.3468</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.214</v>
+        <v>0.1107</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.214</v>
+        <v>-0.4254</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.858</v>
+        <v>-2.2289</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.4675</v>
+        <v>-2.9957</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6095</v>
+        <v>0.7668</v>
       </c>
       <c r="G22" t="n">
         <v>-2.0048</v>
@@ -2170,13 +2170,13 @@
         <v>0.9278</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3892</v>
+        <v>0.2399</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6642</v>
+        <v>-0.1924</v>
       </c>
       <c r="U22" t="n">
-        <v>0.275</v>
+        <v>0.4323</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8874</v>
+        <v>-2.4835</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.0452</v>
+        <v>-2.2811</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8421999999999999</v>
+        <v>-0.2023</v>
       </c>
       <c r="G23" t="n">
         <v>-1.8012</v>
@@ -2248,13 +2248,13 @@
         <v>1.6237</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3361</v>
+        <v>0.0679</v>
       </c>
       <c r="T23" t="n">
-        <v>0.7512</v>
+        <v>0.5153</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.0873</v>
+        <v>-0.4474</v>
       </c>
       <c r="V23" t="n">
         <v>-1.214</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.4499</v>
+        <v>-5.4333</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.9898</v>
+        <v>-6.636</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5399</v>
+        <v>1.2026</v>
       </c>
       <c r="G24" t="n">
         <v>-2.2246</v>
@@ -2326,13 +2326,13 @@
         <v>1.8556</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7639</v>
+        <v>0.2526</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1766</v>
+        <v>0.1772</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5873</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="V24" t="n">
         <v>-0.6778999999999999</v>
@@ -2359,25 +2359,25 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-9.1553</v>
+        <v>-6.0098</v>
       </c>
       <c r="E25" t="n">
-        <v>-13.3595</v>
+        <v>-13.3596</v>
       </c>
       <c r="F25" t="n">
-        <v>4.204400000000001</v>
+        <v>7.3498</v>
       </c>
       <c r="G25" t="n">
         <v>-1.9317</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6786</v>
+        <v>0.6785999999999995</v>
       </c>
       <c r="I25" t="n">
         <v>-2.6101</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.339900000000001</v>
+        <v>-3.339899999999999</v>
       </c>
       <c r="K25" t="n">
         <v>2.6506</v>
@@ -2386,7 +2386,7 @@
         <v>-5.990500000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>1.407999999999999</v>
+        <v>1.408</v>
       </c>
       <c r="N25" t="n">
         <v>-1.9722</v>
@@ -2404,19 +2404,19 @@
         <v>13.9173</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.120100000000001</v>
+        <v>2.0254</v>
       </c>
       <c r="T25" t="n">
-        <v>0.9662999999999996</v>
+        <v>0.9664</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.0866</v>
+        <v>1.0588</v>
       </c>
       <c r="V25" t="n">
         <v>-3.7838</v>
       </c>
       <c r="W25" t="n">
-        <v>5.2503</v>
+        <v>5.250299999999999</v>
       </c>
       <c r="X25" t="n">
         <v>-9.0341</v>
